--- a/project_catalog_data.xlsx
+++ b/project_catalog_data.xlsx
@@ -433,7 +433,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>AI IoT Hydroponics Smart Farming System</v>
+        <v>AI IoT Hydroponics Smart Farming System [Verified Updated]</v>
       </c>
       <c r="B2" t="str">
         <v>IoT</v>
@@ -445,7 +445,7 @@
         <v>Product</v>
       </c>
       <c r="E2">
-        <v>18500</v>
+        <v>9000</v>
       </c>
       <c r="F2" t="str">
         <v>Autonomous hydroponics sensor system with real-time nutrient balancing and cloud analytics.</v>
@@ -460,7 +460,7 @@
         <v>Hydroponics, IoT, ECE, Sensors</v>
       </c>
       <c r="J2" t="str">
-        <v>FALSE</v>
+        <v>TRUE</v>
       </c>
     </row>
     <row r="3">
